--- a/_arquivos/faturamento-canal-distribuidor.xlsx
+++ b/_arquivos/faturamento-canal-distribuidor.xlsx
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.0586</v>
+        <v>0.049</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>13932.72</v>
+        <v>10556.1</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>1180</v>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.0562</v>
+        <v>0.049</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>17743.44</v>
+        <v>15196.98</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>660</v>
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.0576</v>
+        <v>0.049</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>8858.559999999999</v>
+        <v>16090.92</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>660</v>
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.0539</v>
+        <v>0.049</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>6982.22</v>
+        <v>10137.66</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>330</v>
@@ -666,16 +666,16 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.049</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5265.28</v>
+        <v>10556.1</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1180</v>
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.0443</v>
+        <v>0.049</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>10608.27</v>
+        <v>12315.45</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>1180</v>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.0473</v>
+        <v>0.049</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>18806.3</v>
+        <v>15196.98</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>660</v>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.0447</v>
+        <v>0.049</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>8616.809999999999</v>
+        <v>10137.66</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>330</v>
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.0575</v>
+        <v>0.049</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>15692.62</v>
+        <v>10556.1</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1180</v>
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>23022.48</v>
+        <v>15196.98</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>660</v>
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.062</v>
+        <v>0.049</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>8460.76</v>
+        <v>10137.66</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>330</v>
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.0646</v>
+        <v>0.049</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>12655.96</v>
+        <v>10917.48</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>330</v>
@@ -946,16 +946,16 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.0687</v>
+        <v>0.049</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>20674.86</v>
+        <v>15834.15</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1180</v>
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.0718</v>
+        <v>0.049</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>7852.57</v>
+        <v>23242.44</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>660</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>7880.49</v>
+        <v>24136.38</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>660</v>
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.0663</v>
+        <v>0.049</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>7273.52</v>
+        <v>15596.4</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>330</v>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.0523</v>
+        <v>0.049</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>8766.23</v>
+        <v>10556.1</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>1180</v>
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.0505</v>
+        <v>0.049</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>21078.9</v>
+        <v>12315.45</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>1180</v>
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.0494</v>
+        <v>0.049</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>25913.36</v>
+        <v>15196.98</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>660</v>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0526</v>
+        <v>0.049</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>23154.46</v>
+        <v>16090.92</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>660</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8170.89</v>
+        <v>10137.66</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>330</v>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0597</v>
+        <v>0.049</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>19135.1</v>
+        <v>10556.1</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>1180</v>
@@ -1296,16 +1296,16 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.0545</v>
+        <v>0.049</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>23108.02</v>
+        <v>15196.98</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>660</v>
@@ -1331,16 +1331,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>8110.62</v>
+        <v>10137.66</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>330</v>
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0634</v>
+        <v>0.049</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>19059.81</v>
+        <v>14074.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1180</v>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>15842.2</v>
+        <v>18772.74</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>660</v>
@@ -1442,10 +1442,10 @@
         <v>940</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.0629</v>
+        <v>0.049</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>19379.23</v>
+        <v>19666.68</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>660</v>
@@ -1471,16 +1471,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.0664</v>
+        <v>0.049</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>8421.07</v>
+        <v>12867.03</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>330</v>
@@ -1512,10 +1512,10 @@
         <v>1850</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.0467</v>
+        <v>0.049</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10581.63</v>
+        <v>10556.1</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>1180</v>
@@ -1547,10 +1547,10 @@
         <v>940</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.0502</v>
+        <v>0.049</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>15177.8</v>
+        <v>15196.98</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>660</v>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0487</v>
+        <v>0.049</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>16771.42</v>
+        <v>10137.66</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>330</v>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.0483</v>
+        <v>0.049</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>11315.71</v>
+        <v>10917.48</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>330</v>
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.0419</v>
+        <v>0.049</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>7089.94</v>
+        <v>10556.1</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1180</v>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.0423</v>
+        <v>0.049</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>15945.7</v>
+        <v>12315.45</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>1180</v>
@@ -1716,16 +1716,16 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.0422</v>
+        <v>0.049</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>16205.98</v>
+        <v>15196.98</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>660</v>
@@ -1751,16 +1751,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.0444</v>
+        <v>0.049</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>11753.88</v>
+        <v>10137.66</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>330</v>
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.0591</v>
+        <v>0.049</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>6962.66</v>
+        <v>14074.8</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>1180</v>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.0593</v>
+        <v>0.049</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>20883.54</v>
+        <v>15834.15</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>1180</v>
@@ -1856,16 +1856,16 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.0557</v>
+        <v>0.049</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15977.56</v>
+        <v>20560.62</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>660</v>
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.0578</v>
+        <v>0.049</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>16827.69</v>
+        <v>21454.56</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>660</v>
@@ -1926,16 +1926,16 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.049</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>12726.32</v>
+        <v>14036.76</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>330</v>
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.0557</v>
+        <v>0.049</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>6987.82</v>
+        <v>10556.1</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>1180</v>
@@ -1996,16 +1996,16 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.0528</v>
+        <v>0.049</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>14245.89</v>
+        <v>15196.98</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>660</v>
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.0495</v>
+        <v>0.049</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>25910.63</v>
+        <v>16090.92</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>660</v>
@@ -2066,16 +2066,16 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.0546</v>
+        <v>0.049</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>14729.33</v>
+        <v>10137.66</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>330</v>
@@ -2101,16 +2101,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.0639</v>
+        <v>0.049</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>20781.42</v>
+        <v>10556.1</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>1180</v>
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.0583</v>
+        <v>0.049</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>19474.36</v>
+        <v>15196.98</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>660</v>
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.0631</v>
+        <v>0.049</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>10371.48</v>
+        <v>10137.66</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>330</v>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.0512</v>
+        <v>0.05</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>14042.24</v>
+        <v>10545</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>1180</v>
@@ -2241,16 +2241,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.0538</v>
+        <v>0.05</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>19567.42</v>
+        <v>16074</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>660</v>
@@ -2276,16 +2276,16 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0.0519</v>
+        <v>0.05</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>24062.78</v>
+        <v>16074</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>660</v>
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.0527</v>
+        <v>0.05</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>6214.29</v>
+        <v>10516.5</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>330</v>
@@ -2346,16 +2346,16 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0483</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>12367.25</v>
+        <v>10563.5</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>1180</v>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.0472</v>
+        <v>0.0483</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>10576.08</v>
+        <v>12324.08</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>1180</v>
@@ -2416,16 +2416,16 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.0483</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>20655.75</v>
+        <v>16102.2</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>660</v>
@@ -2451,16 +2451,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.0472</v>
+        <v>0.0483</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>11328.79</v>
+        <v>10534.95</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>330</v>
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>0.0641</v>
+        <v>0.0505</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>12119.9</v>
+        <v>10539.45</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>1180</v>
@@ -2521,16 +2521,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.0639</v>
+        <v>0.0505</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>18478.61</v>
+        <v>16065.54</v>
       </c>
       <c r="I59" s="5" t="n">
         <v>660</v>
@@ -2556,16 +2556,16 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0505</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>8838.74</v>
+        <v>10510.97</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>330</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.0625</v>
+        <v>0.0505</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>9993.75</v>
+        <v>10900.26</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>330</v>
@@ -2626,16 +2626,16 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0.0717</v>
+        <v>0.049</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>15456.19</v>
+        <v>17593.5</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>1180</v>
@@ -2661,16 +2661,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>10550.18</v>
+        <v>23242.44</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>660</v>
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>0.0659</v>
+        <v>0.049</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>10536.65</v>
+        <v>25030.32</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>660</v>
@@ -2731,16 +2731,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>0.0641</v>
+        <v>0.049</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>8441.82</v>
+        <v>15986.31</v>
       </c>
       <c r="I65" s="5" t="n">
         <v>330</v>
@@ -2766,16 +2766,16 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.0495</v>
+        <v>0.0498</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>21101.1</v>
+        <v>10546.85</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>1180</v>
@@ -2807,10 +2807,10 @@
         <v>1850</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>0.048</v>
+        <v>0.0498</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>12328.4</v>
+        <v>12304.66</v>
       </c>
       <c r="I67" s="5" t="n">
         <v>1180</v>
@@ -2836,16 +2836,16 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>0.0523</v>
+        <v>0.0498</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>18707.6</v>
+        <v>16076.82</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>660</v>
@@ -2871,16 +2871,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F69" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>0.0525</v>
+        <v>0.0498</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>24047.55</v>
+        <v>16076.82</v>
       </c>
       <c r="I69" s="5" t="n">
         <v>660</v>
@@ -2906,16 +2906,16 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0.049</v>
+        <v>0.0498</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>17545.95</v>
+        <v>10518.35</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>330</v>
@@ -2941,16 +2941,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>0.0616</v>
+        <v>0.048</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>19096.44</v>
+        <v>10567.2</v>
       </c>
       <c r="I71" s="5" t="n">
         <v>1180</v>
@@ -2976,16 +2976,16 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.0594</v>
+        <v>0.048</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>24756.59</v>
+        <v>16107.84</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>660</v>
@@ -3011,16 +3011,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>0.0577</v>
+        <v>0.048</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>6181.49</v>
+        <v>10538.64</v>
       </c>
       <c r="I73" s="5" t="n">
         <v>330</v>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F74" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>0.0631</v>
+        <v>0.049</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>19065.92</v>
+        <v>14074.8</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>1180</v>
@@ -3081,16 +3081,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>17611.84</v>
+        <v>19666.68</v>
       </c>
       <c r="I75" s="5" t="n">
         <v>660</v>
@@ -3122,10 +3122,10 @@
         <v>940</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>20212.54</v>
+        <v>20560.62</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>660</v>
@@ -3151,16 +3151,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F77" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>0.0615</v>
+        <v>0.049</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>6156.56</v>
+        <v>13256.94</v>
       </c>
       <c r="I77" s="5" t="n">
         <v>330</v>
@@ -3192,10 +3192,10 @@
         <v>1850</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>0.0495</v>
+        <v>0.0502</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>10550.55</v>
+        <v>10543.15</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>1180</v>
@@ -3221,16 +3221,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F79" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>0.0487</v>
+        <v>0.0502</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>9836.440000000001</v>
+        <v>16071.18</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>660</v>
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.0468</v>
+        <v>0.0502</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>6252.99</v>
+        <v>10514.65</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>330</v>
@@ -3291,16 +3291,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>0.0472</v>
+        <v>0.0502</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>12891.38</v>
+        <v>10904.09</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>330</v>
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F82" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.0486</v>
+        <v>0.0485</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>7040.36</v>
+        <v>10561.65</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>1180</v>
@@ -3361,16 +3361,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>0.0412</v>
+        <v>0.0485</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>21285.36</v>
+        <v>12321.92</v>
       </c>
       <c r="I83" s="5" t="n">
         <v>1180</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F84" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.0459</v>
+        <v>0.0485</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>12555.96</v>
+        <v>16099.38</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>660</v>
@@ -3431,16 +3431,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>0.0461</v>
+        <v>0.0485</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>7430.88</v>
+        <v>10533.1</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>330</v>
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F86" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.0578</v>
+        <v>0.049</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>13944.56</v>
+        <v>15834.15</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>1180</v>
@@ -3501,16 +3501,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F87" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>0.054</v>
+        <v>0.049</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>17501</v>
+        <v>15834.15</v>
       </c>
       <c r="I87" s="5" t="n">
         <v>1180</v>
@@ -3536,16 +3536,16 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F88" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.0609</v>
+        <v>0.049</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>20303.34</v>
+        <v>21454.56</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>660</v>
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>0.0568</v>
+        <v>0.049</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>19505.38</v>
+        <v>22348.5</v>
       </c>
       <c r="I89" s="5" t="n">
         <v>660</v>
@@ -3606,16 +3606,16 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F90" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.0537</v>
+        <v>0.049</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>9311.59</v>
+        <v>14426.67</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>330</v>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>0.055</v>
+        <v>0.0503</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>6993</v>
+        <v>10541.3</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>1180</v>
@@ -3676,16 +3676,16 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>14245.89</v>
+        <v>16068.36</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>660</v>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>940</v>
@@ -3720,7 +3720,7 @@
         <v>0.0503</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>26781.54</v>
+        <v>16068.36</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>660</v>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F94" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.0506</v>
+        <v>0.0503</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>5838.81</v>
+        <v>10512.81</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>330</v>
@@ -3781,16 +3781,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F95" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>0.0589</v>
+        <v>0.0497</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>19151.39</v>
+        <v>10548.7</v>
       </c>
       <c r="I95" s="5" t="n">
         <v>1180</v>
@@ -3816,16 +3816,16 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F96" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.0603</v>
+        <v>0.0497</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>26499.54</v>
+        <v>16079.64</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>660</v>
@@ -3851,16 +3851,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F97" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>0.0621</v>
+        <v>0.0497</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>5768.09</v>
+        <v>10520.19</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>330</v>
@@ -3886,16 +3886,16 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F98" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0.0588</v>
+        <v>0.051</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>12188.54</v>
+        <v>10533.9</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>1180</v>
@@ -3921,16 +3921,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>0.0566</v>
+        <v>0.051</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>8867.959999999999</v>
+        <v>14272.96</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>660</v>
@@ -3956,16 +3956,16 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0.0551</v>
+        <v>0.051</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>14211.3</v>
+        <v>15165.02</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>660</v>
@@ -3991,16 +3991,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>0.0523</v>
+        <v>0.051</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>17096.51</v>
+        <v>9727.25</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>330</v>
@@ -4032,10 +4032,10 @@
         <v>1850</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.0477</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>10563.87</v>
+        <v>10570.9</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>1180</v>
@@ -4061,16 +4061,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F103" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>0.0466</v>
+        <v>0.0477</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>19401.69</v>
+        <v>10570.9</v>
       </c>
       <c r="I103" s="5" t="n">
         <v>1180</v>
@@ -4096,16 +4096,16 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.0489</v>
+        <v>0.0477</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>13410.51</v>
+        <v>14323.09</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>660</v>
@@ -4131,16 +4131,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F105" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>0.0519</v>
+        <v>0.0477</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>15548.84</v>
+        <v>9761.42</v>
       </c>
       <c r="I105" s="5" t="n">
         <v>330</v>
@@ -4172,10 +4172,10 @@
         <v>1850</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.0634</v>
+        <v>0.052</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>10396.26</v>
+        <v>10522.8</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>1180</v>
@@ -4201,16 +4201,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>0.0629</v>
+        <v>0.052</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>17617.48</v>
+        <v>14257.92</v>
       </c>
       <c r="I107" s="5" t="n">
         <v>660</v>
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0.0586</v>
+        <v>0.052</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>8491.43</v>
+        <v>9717</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>330</v>
@@ -4271,16 +4271,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>0.0598</v>
+        <v>0.052</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>11564.46</v>
+        <v>10105.68</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>330</v>
@@ -4306,16 +4306,16 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>5150.95</v>
+        <v>15834.15</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>1180</v>
@@ -4341,16 +4341,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>0.0678</v>
+        <v>0.049</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>14020.29</v>
+        <v>21454.56</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>660</v>
@@ -4376,16 +4376,16 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>12245.38</v>
+        <v>22348.5</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>660</v>
@@ -4411,16 +4411,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F113" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>0.0668</v>
+        <v>0.049</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>17217.54</v>
+        <v>14426.67</v>
       </c>
       <c r="I113" s="5" t="n">
         <v>330</v>
@@ -4446,16 +4446,16 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0507</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>13977.12</v>
+        <v>10537.6</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>1180</v>
@@ -4481,16 +4481,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>0.0486</v>
+        <v>0.0507</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>14080.72</v>
+        <v>10537.6</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>1180</v>
@@ -4516,16 +4516,16 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>0.0498</v>
+        <v>0.0507</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>9825.07</v>
+        <v>14277.97</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>660</v>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F117" s="5" t="n">
         <v>940</v>
@@ -4560,7 +4560,7 @@
         <v>0.0507</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>12492.79</v>
+        <v>15170.35</v>
       </c>
       <c r="I117" s="5" t="n">
         <v>660</v>
@@ -4586,16 +4586,16 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.053</v>
+        <v>0.0507</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>11648.1</v>
+        <v>9730.67</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>330</v>
@@ -4621,16 +4621,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F119" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>0.0607</v>
+        <v>0.047</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>20852.46</v>
+        <v>10578.3</v>
       </c>
       <c r="I119" s="5" t="n">
         <v>1180</v>
@@ -4656,16 +4656,16 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.0613</v>
+        <v>0.047</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>20294.69</v>
+        <v>14333.12</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>660</v>
@@ -4691,16 +4691,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F121" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>0.0604</v>
+        <v>0.047</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>10016.14</v>
+        <v>9768.25</v>
       </c>
       <c r="I121" s="5" t="n">
         <v>330</v>
@@ -4726,16 +4726,16 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F122" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.0667</v>
+        <v>0.049</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>6906.42</v>
+        <v>12315.45</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>1180</v>
@@ -4761,16 +4761,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F123" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>0.0673</v>
+        <v>0.049</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>9644.120000000001</v>
+        <v>17878.8</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>660</v>
@@ -4796,16 +4796,16 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>0.066</v>
+        <v>0.049</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>26338.8</v>
+        <v>18772.74</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>660</v>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F125" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>11474.67</v>
+        <v>12087.21</v>
       </c>
       <c r="I125" s="5" t="n">
         <v>330</v>
@@ -4866,16 +4866,16 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.0523</v>
+        <v>0.0513</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>15779.2</v>
+        <v>10530.2</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>1180</v>
@@ -4901,16 +4901,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F127" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>0.0467</v>
+        <v>0.0513</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>16129.84</v>
+        <v>14267.95</v>
       </c>
       <c r="I127" s="5" t="n">
         <v>660</v>
@@ -4936,16 +4936,16 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F128" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>0.0538</v>
+        <v>0.0513</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>17457.39</v>
+        <v>9723.83</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>330</v>
@@ -4971,16 +4971,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F129" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>0.0497</v>
+        <v>0.0513</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>10519.82</v>
+        <v>10112.79</v>
       </c>
       <c r="I129" s="5" t="n">
         <v>330</v>
@@ -5006,16 +5006,16 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.0468</v>
+        <v>0.048</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>7053.68</v>
+        <v>10567.2</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>1180</v>
@@ -5041,16 +5041,16 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F131" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>0.0489</v>
+        <v>0.048</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>8797.68</v>
+        <v>10567.2</v>
       </c>
       <c r="I131" s="5" t="n">
         <v>1180</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F132" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>0.0422</v>
+        <v>0.048</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>7202.66</v>
+        <v>14318.08</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>660</v>
@@ -5111,16 +5111,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F133" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G133" s="6" t="n">
-        <v>0.0447</v>
+        <v>0.048</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>16841.94</v>
+        <v>9758</v>
       </c>
       <c r="I133" s="5" t="n">
         <v>330</v>
@@ -5146,16 +5146,16 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.0579</v>
+        <v>0.049</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>8714.43</v>
+        <v>14074.8</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>1180</v>
@@ -5181,16 +5181,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F135" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G135" s="6" t="n">
-        <v>0.0608</v>
+        <v>0.049</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>20850.24</v>
+        <v>14074.8</v>
       </c>
       <c r="I135" s="5" t="n">
         <v>1180</v>
@@ -5216,16 +5216,16 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F136" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>0.0605</v>
+        <v>0.049</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>25610.77</v>
+        <v>18772.74</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>660</v>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F137" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>0.0574</v>
+        <v>0.049</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>10632.53</v>
+        <v>19666.68</v>
       </c>
       <c r="I137" s="5" t="n">
         <v>660</v>
@@ -5286,16 +5286,16 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F138" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0.0532</v>
+        <v>0.049</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>7375.57</v>
+        <v>12867.03</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>330</v>
@@ -5321,16 +5321,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F139" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G139" s="6" t="n">
-        <v>0.0532</v>
+        <v>0.0517</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>7006.32</v>
+        <v>10526.5</v>
       </c>
       <c r="I139" s="5" t="n">
         <v>1180</v>
@@ -5356,16 +5356,16 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F140" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.0525</v>
+        <v>0.0517</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>10687.8</v>
+        <v>14262.93</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>660</v>
@@ -5391,16 +5391,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F141" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>0.0556</v>
+        <v>0.0517</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>12428.3</v>
+        <v>15154.37</v>
       </c>
       <c r="I141" s="5" t="n">
         <v>660</v>
@@ -5426,16 +5426,16 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F142" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0517</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>8186.39</v>
+        <v>9720.42</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>330</v>
@@ -5467,10 +5467,10 @@
         <v>1850</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>0.0583</v>
+        <v>0.0503</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>10452.87</v>
+        <v>10541.3</v>
       </c>
       <c r="I143" s="5" t="n">
         <v>1180</v>
@@ -5496,16 +5496,16 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F144" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>0.0621</v>
+        <v>0.0503</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>13224.39</v>
+        <v>14282.99</v>
       </c>
       <c r="I144" s="3" t="n">
         <v>660</v>
@@ -5537,10 +5537,10 @@
         <v>410</v>
       </c>
       <c r="G145" s="6" t="n">
-        <v>0.0581</v>
+        <v>0.0503</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>9654.48</v>
+        <v>9734.08</v>
       </c>
       <c r="I145" s="5" t="n">
         <v>330</v>
@@ -5566,16 +5566,16 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F146" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>0.0577</v>
+        <v>0.052</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>15689.3</v>
+        <v>10522.8</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>1180</v>
@@ -5601,16 +5601,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F147" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G147" s="6" t="n">
-        <v>0.0583</v>
+        <v>0.052</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>7966.78</v>
+        <v>14257.92</v>
       </c>
       <c r="I147" s="5" t="n">
         <v>660</v>
@@ -5636,16 +5636,16 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F148" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>0.0582</v>
+        <v>0.052</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>16820.55</v>
+        <v>14257.92</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>660</v>
@@ -5671,16 +5671,16 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F149" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>0.0557</v>
+        <v>0.052</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>13937.87</v>
+        <v>9328.32</v>
       </c>
       <c r="I149" s="5" t="n">
         <v>330</v>
@@ -5706,16 +5706,16 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F150" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>0.0474</v>
+        <v>0.047</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>19385.41</v>
+        <v>10578.3</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>1180</v>
@@ -5741,16 +5741,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F151" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G151" s="6" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>19434.25</v>
+        <v>10578.3</v>
       </c>
       <c r="I151" s="5" t="n">
         <v>1180</v>
@@ -5776,16 +5776,16 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F152" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.047</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>10736.3</v>
+        <v>14333.12</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>660</v>
@@ -5811,16 +5811,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F153" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G153" s="6" t="n">
-        <v>0.051</v>
+        <v>0.047</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>5836.35</v>
+        <v>9377.52</v>
       </c>
       <c r="I153" s="5" t="n">
         <v>330</v>
@@ -5846,16 +5846,16 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F154" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>0.0619</v>
+        <v>0.0535</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>8677.43</v>
+        <v>10506.15</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>1180</v>
@@ -5881,16 +5881,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F155" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G155" s="6" t="n">
-        <v>0.0584</v>
+        <v>0.0535</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>10621.25</v>
+        <v>14235.36</v>
       </c>
       <c r="I155" s="5" t="n">
         <v>660</v>
@@ -5916,16 +5916,16 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F156" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0535</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>11537.4</v>
+        <v>9313.559999999999</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>330</v>
@@ -5951,16 +5951,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F157" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G157" s="6" t="n">
-        <v>0.0615</v>
+        <v>0.0535</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>6926.13</v>
+        <v>9701.620000000001</v>
       </c>
       <c r="I157" s="5" t="n">
         <v>330</v>
@@ -5992,10 +5992,10 @@
         <v>1850</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0755</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>13327.4</v>
+        <v>13682.6</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>1180</v>
@@ -6021,16 +6021,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F159" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G159" s="6" t="n">
-        <v>0.0984</v>
+        <v>0.0755</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>20340.1</v>
+        <v>19987.69</v>
       </c>
       <c r="I159" s="5" t="n">
         <v>660</v>
@@ -6056,16 +6056,16 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F160" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>0.1011</v>
+        <v>0.0755</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>9294.629999999999</v>
+        <v>20856.72</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>660</v>
@@ -6091,16 +6091,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F161" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G161" s="6" t="n">
-        <v>0.096</v>
+        <v>0.0755</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>5930.24</v>
+        <v>13645.62</v>
       </c>
       <c r="I161" s="5" t="n">
         <v>330</v>
@@ -6126,16 +6126,16 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F162" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.0515</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>12324.51</v>
+        <v>10528.35</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>1180</v>
@@ -6161,16 +6161,16 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F163" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G163" s="6" t="n">
-        <v>0.0521</v>
+        <v>0.0515</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>7014.46</v>
+        <v>10528.35</v>
       </c>
       <c r="I163" s="5" t="n">
         <v>1180</v>
@@ -6196,16 +6196,16 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F164" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.0515</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>22367.3</v>
+        <v>14265.44</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>660</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F165" s="5" t="n">
         <v>940</v>
@@ -6240,7 +6240,7 @@
         <v>0.0515</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>8915.9</v>
+        <v>14265.44</v>
       </c>
       <c r="I165" s="5" t="n">
         <v>660</v>
@@ -6266,16 +6266,16 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F166" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>0.0558</v>
+        <v>0.0515</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>13162.15</v>
+        <v>9333.24</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>330</v>
@@ -6301,16 +6301,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F167" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G167" s="6" t="n">
-        <v>0.0581</v>
+        <v>0.046</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>20910.18</v>
+        <v>10589.4</v>
       </c>
       <c r="I167" s="5" t="n">
         <v>1180</v>
@@ -6336,16 +6336,16 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F168" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>0.0562</v>
+        <v>0.046</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>26615.16</v>
+        <v>14348.16</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>660</v>
@@ -6371,16 +6371,16 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F169" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G169" s="6" t="n">
-        <v>0.0583</v>
+        <v>0.046</v>
       </c>
       <c r="H169" s="5" t="n">
-        <v>11969.01</v>
+        <v>9387.360000000001</v>
       </c>
       <c r="I169" s="5" t="n">
         <v>330</v>
@@ -6406,16 +6406,16 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F170" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>0.0941</v>
+        <v>0.0805</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>16759.15</v>
+        <v>11907.52</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>1180</v>
@@ -6441,16 +6441,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F171" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G171" s="6" t="n">
-        <v>0.0956</v>
+        <v>0.0805</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>12752.04</v>
+        <v>16422.27</v>
       </c>
       <c r="I171" s="5" t="n">
         <v>660</v>
@@ -6476,16 +6476,16 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F172" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>0.0974</v>
+        <v>0.0805</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>13575.1</v>
+        <v>17286.6</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>660</v>
@@ -6511,16 +6511,16 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F173" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G173" s="6" t="n">
-        <v>0.0975</v>
+        <v>0.0805</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>15911.07</v>
+        <v>11309.85</v>
       </c>
       <c r="I173" s="5" t="n">
         <v>330</v>
@@ -6546,16 +6546,16 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F174" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>0.0471</v>
+        <v>0.0525</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>17628.65</v>
+        <v>10517.25</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>1180</v>
@@ -6581,16 +6581,16 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F175" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G175" s="6" t="n">
-        <v>0.0491</v>
+        <v>0.0525</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>9832.309999999999</v>
+        <v>14250.4</v>
       </c>
       <c r="I175" s="5" t="n">
         <v>660</v>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F176" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>0.0466</v>
+        <v>0.0525</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>9772.35</v>
+        <v>9323.4</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>330</v>
@@ -6651,16 +6651,16 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F177" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G177" s="6" t="n">
-        <v>0.0494</v>
+        <v>0.0525</v>
       </c>
       <c r="H177" s="5" t="n">
-        <v>8574.41</v>
+        <v>9711.879999999999</v>
       </c>
       <c r="I177" s="5" t="n">
         <v>330</v>
@@ -6692,10 +6692,10 @@
         <v>1850</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>0.0464</v>
+        <v>0.0475</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>10584.96</v>
+        <v>10572.75</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>1180</v>
@@ -6721,16 +6721,16 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F179" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G179" s="6" t="n">
-        <v>0.0482</v>
+        <v>0.0475</v>
       </c>
       <c r="H179" s="5" t="n">
-        <v>7043.32</v>
+        <v>10572.75</v>
       </c>
       <c r="I179" s="5" t="n">
         <v>1180</v>
@@ -6756,16 +6756,16 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F180" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>0.0485</v>
+        <v>0.0475</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>10732.92</v>
+        <v>14325.6</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>660</v>
@@ -6791,16 +6791,16 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F181" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G181" s="6" t="n">
-        <v>0.0463</v>
+        <v>0.0475</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>13685.59</v>
+        <v>9372.6</v>
       </c>
       <c r="I181" s="5" t="n">
         <v>330</v>
@@ -6826,16 +6826,16 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F182" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>0.055</v>
+        <v>0.049</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>8741.25</v>
+        <v>10556.1</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>1180</v>
@@ -6857,23 +6857,23 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Padrão</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>940</v>
+        <v>1850</v>
       </c>
       <c r="G183" s="6" t="n">
-        <v>0.0607</v>
+        <v>0.049</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>10595.3</v>
+        <v>10556.1</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>660</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="184">
@@ -6896,16 +6896,16 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F184" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>0.059</v>
+        <v>0.049</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>13268.1</v>
+        <v>18772.74</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>660</v>
@@ -6927,23 +6927,23 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Padrão</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>410</v>
+        <v>940</v>
       </c>
       <c r="G185" s="6" t="n">
-        <v>0.0562</v>
+        <v>0.049</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>6965.24</v>
+        <v>19666.68</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="186">
@@ -6966,16 +6966,16 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F186" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>0.0543</v>
+        <v>0.049</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>11632.11</v>
+        <v>22224.87</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>330</v>
@@ -7007,10 +7007,10 @@
         <v>1850</v>
       </c>
       <c r="G187" s="6" t="n">
-        <v>0.0503</v>
+        <v>0.053</v>
       </c>
       <c r="H187" s="5" t="n">
-        <v>10541.67</v>
+        <v>10511.7</v>
       </c>
       <c r="I187" s="5" t="n">
         <v>1180</v>
@@ -7036,16 +7036,16 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F188" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G188" s="4" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>18614.82</v>
+        <v>14242.88</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>660</v>
@@ -7071,16 +7071,16 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F189" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G189" s="6" t="n">
-        <v>0.0517</v>
+        <v>0.053</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>17828.04</v>
+        <v>14242.88</v>
       </c>
       <c r="I189" s="5" t="n">
         <v>660</v>
@@ -7106,16 +7106,16 @@
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F190" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G190" s="4" t="n">
-        <v>0.0519</v>
+        <v>0.053</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>8163.14</v>
+        <v>9318.48</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>330</v>
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F191" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G191" s="6" t="n">
-        <v>0.0618</v>
+        <v>0.051</v>
       </c>
       <c r="H191" s="5" t="n">
-        <v>6942.68</v>
+        <v>10533.9</v>
       </c>
       <c r="I191" s="5" t="n">
         <v>1180</v>
@@ -7176,16 +7176,16 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F192" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G192" s="4" t="n">
-        <v>0.0587</v>
+        <v>0.051</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>7078.58</v>
+        <v>14272.96</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>660</v>
@@ -7211,16 +7211,16 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F193" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G193" s="6" t="n">
-        <v>0.0595</v>
+        <v>0.051</v>
       </c>
       <c r="H193" s="5" t="n">
-        <v>11182.55</v>
+        <v>9338.16</v>
       </c>
       <c r="I193" s="5" t="n">
         <v>330</v>
@@ -7246,16 +7246,16 @@
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F194" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G194" s="4" t="n">
-        <v>0.0541</v>
+        <v>0.053</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>5249.74</v>
+        <v>10511.7</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>1180</v>
@@ -7281,16 +7281,16 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F195" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G195" s="6" t="n">
-        <v>0.056</v>
+        <v>0.053</v>
       </c>
       <c r="H195" s="5" t="n">
-        <v>21296.64</v>
+        <v>14242.88</v>
       </c>
       <c r="I195" s="5" t="n">
         <v>660</v>
@@ -7316,16 +7316,16 @@
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F196" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G196" s="4" t="n">
-        <v>0.0587</v>
+        <v>0.053</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>21235.73</v>
+        <v>15133.06</v>
       </c>
       <c r="I196" s="3" t="n">
         <v>660</v>
@@ -7351,16 +7351,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F197" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G197" s="6" t="n">
-        <v>0.0589</v>
+        <v>0.053</v>
       </c>
       <c r="H197" s="5" t="n">
-        <v>6945.32</v>
+        <v>9706.75</v>
       </c>
       <c r="I197" s="5" t="n">
         <v>330</v>
@@ -7392,10 +7392,10 @@
         <v>1850</v>
       </c>
       <c r="G198" s="4" t="n">
-        <v>0.0518</v>
+        <v>0.0463</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>10525.02</v>
+        <v>10585.7</v>
       </c>
       <c r="I198" s="3" t="n">
         <v>1180</v>
@@ -7421,16 +7421,16 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F199" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G199" s="6" t="n">
-        <v>0.0447</v>
+        <v>0.0463</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>7069.22</v>
+        <v>10585.7</v>
       </c>
       <c r="I199" s="5" t="n">
         <v>1180</v>
@@ -7462,10 +7462,10 @@
         <v>940</v>
       </c>
       <c r="G200" s="4" t="n">
-        <v>0.0443</v>
+        <v>0.0463</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>14373.73</v>
+        <v>14343.15</v>
       </c>
       <c r="I200" s="3" t="n">
         <v>660</v>
@@ -7491,16 +7491,16 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F201" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G201" s="6" t="n">
-        <v>0.0455</v>
+        <v>0.0463</v>
       </c>
       <c r="H201" s="5" t="n">
-        <v>15262.45</v>
+        <v>9775.08</v>
       </c>
       <c r="I201" s="5" t="n">
         <v>330</v>
@@ -7526,16 +7526,16 @@
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F202" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G202" s="4" t="n">
-        <v>0.0636</v>
+        <v>0.055</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>8661.700000000001</v>
+        <v>10489.5</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>1180</v>
@@ -7561,16 +7561,16 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F203" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G203" s="6" t="n">
-        <v>0.0636</v>
+        <v>0.055</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>25526.26</v>
+        <v>14212.8</v>
       </c>
       <c r="I203" s="5" t="n">
         <v>660</v>
@@ -7596,16 +7596,16 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F204" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G204" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.055</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>8862.309999999999</v>
+        <v>9686.25</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>330</v>
@@ -7631,16 +7631,16 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F205" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G205" s="6" t="n">
-        <v>0.0644</v>
+        <v>0.055</v>
       </c>
       <c r="H205" s="5" t="n">
-        <v>12275.07</v>
+        <v>10461.15</v>
       </c>
       <c r="I205" s="5" t="n">
         <v>330</v>
@@ -7666,16 +7666,16 @@
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F206" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G206" s="4" t="n">
-        <v>0.128</v>
+        <v>0.102</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>19358.4</v>
+        <v>14951.7</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>1180</v>
@@ -7701,16 +7701,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F207" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G207" s="6" t="n">
-        <v>0.1247</v>
+        <v>0.102</v>
       </c>
       <c r="H207" s="5" t="n">
-        <v>14810.08</v>
+        <v>21103</v>
       </c>
       <c r="I207" s="5" t="n">
         <v>660</v>
@@ -7736,16 +7736,16 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F208" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G208" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.102</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>7356.82</v>
+        <v>21947.12</v>
       </c>
       <c r="I208" s="3" t="n">
         <v>660</v>
@@ -7771,16 +7771,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F209" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G209" s="6" t="n">
-        <v>0.1274</v>
+        <v>0.102</v>
       </c>
       <c r="H209" s="5" t="n">
-        <v>7155.32</v>
+        <v>13990.84</v>
       </c>
       <c r="I209" s="5" t="n">
         <v>330</v>
@@ -7806,16 +7806,16 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F210" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G210" s="4" t="n">
-        <v>0.0502</v>
+        <v>0.0523</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>7028.52</v>
+        <v>10519.1</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>1180</v>
@@ -7841,16 +7841,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F211" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G211" s="6" t="n">
-        <v>0.0531</v>
+        <v>0.0523</v>
       </c>
       <c r="H211" s="5" t="n">
-        <v>5255.3</v>
+        <v>10519.1</v>
       </c>
       <c r="I211" s="5" t="n">
         <v>1180</v>
@@ -7882,10 +7882,10 @@
         <v>940</v>
       </c>
       <c r="G212" s="4" t="n">
-        <v>0.0487</v>
+        <v>0.0523</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>14307.55</v>
+        <v>14252.91</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>660</v>
@@ -7911,16 +7911,16 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F213" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G213" s="6" t="n">
-        <v>0.0485</v>
+        <v>0.0523</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>13416.15</v>
+        <v>15143.71</v>
       </c>
       <c r="I213" s="5" t="n">
         <v>660</v>
@@ -7946,16 +7946,16 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F214" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G214" s="4" t="n">
-        <v>0.049</v>
+        <v>0.0523</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>16376.22</v>
+        <v>9713.58</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>330</v>
@@ -7981,16 +7981,16 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F215" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G215" s="6" t="n">
-        <v>0.0567</v>
+        <v>0.045</v>
       </c>
       <c r="H215" s="5" t="n">
-        <v>5235.32</v>
+        <v>10600.5</v>
       </c>
       <c r="I215" s="5" t="n">
         <v>1180</v>
@@ -8016,16 +8016,16 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F216" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G216" s="4" t="n">
-        <v>0.0573</v>
+        <v>0.045</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>22153.45</v>
+        <v>14363.2</v>
       </c>
       <c r="I216" s="3" t="n">
         <v>660</v>
@@ -8051,16 +8051,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F217" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G217" s="6" t="n">
-        <v>0.0561</v>
+        <v>0.045</v>
       </c>
       <c r="H217" s="5" t="n">
-        <v>17027.96</v>
+        <v>9788.75</v>
       </c>
       <c r="I217" s="5" t="n">
         <v>330</v>
@@ -8086,16 +8086,16 @@
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F218" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>0.1203</v>
+        <v>0.112</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>8137.23</v>
+        <v>11499.6</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>1180</v>
@@ -8121,16 +8121,16 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F219" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G219" s="6" t="n">
-        <v>0.1219</v>
+        <v>0.112</v>
       </c>
       <c r="H219" s="5" t="n">
-        <v>24762.42</v>
+        <v>17529.12</v>
       </c>
       <c r="I219" s="5" t="n">
         <v>660</v>
@@ -8156,16 +8156,16 @@
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F220" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G220" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.112</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>9018.549999999999</v>
+        <v>17529.12</v>
       </c>
       <c r="I220" s="3" t="n">
         <v>660</v>
@@ -8191,16 +8191,16 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F221" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G221" s="6" t="n">
-        <v>0.1204</v>
+        <v>0.112</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>8294.629999999999</v>
+        <v>11650.56</v>
       </c>
       <c r="I221" s="5" t="n">
         <v>330</v>
@@ -8232,10 +8232,10 @@
         <v>1850</v>
       </c>
       <c r="G222" s="4" t="n">
-        <v>0.0535</v>
+        <v>0.0537</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>10506.15</v>
+        <v>10504.3</v>
       </c>
       <c r="I222" s="3" t="n">
         <v>1180</v>
@@ -8261,16 +8261,16 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F223" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G223" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.0537</v>
       </c>
       <c r="H223" s="5" t="n">
-        <v>25046.11</v>
+        <v>14232.85</v>
       </c>
       <c r="I223" s="5" t="n">
         <v>660</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F224" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G224" s="4" t="n">
-        <v>0.0476</v>
+        <v>0.0537</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>15228.88</v>
+        <v>9699.92</v>
       </c>
       <c r="I224" s="3" t="n">
         <v>330</v>
@@ -8331,16 +8331,16 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F225" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G225" s="6" t="n">
-        <v>0.05</v>
+        <v>0.0537</v>
       </c>
       <c r="H225" s="5" t="n">
-        <v>11295.5</v>
+        <v>10475.91</v>
       </c>
       <c r="I225" s="5" t="n">
         <v>330</v>
@@ -8366,16 +8366,16 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F226" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G226" s="4" t="n">
-        <v>0.0432</v>
+        <v>0.047</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>8850.4</v>
+        <v>10578.3</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>1180</v>
@@ -8401,16 +8401,16 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F227" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G227" s="6" t="n">
-        <v>0.049</v>
+        <v>0.047</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>5278.05</v>
+        <v>10578.3</v>
       </c>
       <c r="I227" s="5" t="n">
         <v>1180</v>
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F228" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G228" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.047</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>8112.29</v>
+        <v>14333.12</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>660</v>
@@ -8471,16 +8471,16 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F229" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G229" s="6" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="H229" s="5" t="n">
-        <v>14878.9</v>
+        <v>9768.25</v>
       </c>
       <c r="I229" s="5" t="n">
         <v>330</v>
@@ -8502,23 +8502,23 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Padrão</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>940</v>
+        <v>1850</v>
       </c>
       <c r="G230" s="4" t="n">
-        <v>0.0571</v>
+        <v>0.049</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>12408.56</v>
+        <v>7037.4</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>660</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="231">
@@ -8537,23 +8537,23 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Padrão</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F231" s="5" t="n">
-        <v>940</v>
+        <v>1850</v>
       </c>
       <c r="G231" s="6" t="n">
-        <v>0.0605</v>
+        <v>0.049</v>
       </c>
       <c r="H231" s="5" t="n">
-        <v>13246.95</v>
+        <v>8796.75</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>660</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="232">
@@ -8572,23 +8572,23 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Padrão</t>
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>410</v>
+        <v>940</v>
       </c>
       <c r="G232" s="4" t="n">
-        <v>0.0583</v>
+        <v>0.049</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>6949.75</v>
+        <v>19666.68</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="233">
@@ -8607,23 +8607,23 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Padrão</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F233" s="5" t="n">
-        <v>410</v>
+        <v>940</v>
       </c>
       <c r="G233" s="6" t="n">
-        <v>0.0565</v>
+        <v>0.049</v>
       </c>
       <c r="H233" s="5" t="n">
-        <v>13539.23</v>
+        <v>20560.62</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="234">
@@ -8646,16 +8646,16 @@
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="F234" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G234" s="4" t="n">
-        <v>0.0574</v>
+        <v>0.049</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>11593.98</v>
+        <v>33532.26</v>
       </c>
       <c r="I234" s="3" t="n">
         <v>330</v>
@@ -8681,16 +8681,16 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F235" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G235" s="6" t="n">
-        <v>0.0568</v>
+        <v>0.0543</v>
       </c>
       <c r="H235" s="5" t="n">
-        <v>15704.28</v>
+        <v>10496.9</v>
       </c>
       <c r="I235" s="5" t="n">
         <v>1180</v>
@@ -8716,16 +8716,16 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F236" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G236" s="4" t="n">
-        <v>0.0545</v>
+        <v>0.0543</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>15109.09</v>
+        <v>14222.83</v>
       </c>
       <c r="I236" s="3" t="n">
         <v>660</v>
@@ -8751,16 +8751,16 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F237" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G237" s="6" t="n">
-        <v>0.0517</v>
+        <v>0.0543</v>
       </c>
       <c r="H237" s="5" t="n">
-        <v>13371.03</v>
+        <v>15111.75</v>
       </c>
       <c r="I237" s="5" t="n">
         <v>660</v>
@@ -8786,16 +8786,16 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F238" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G238" s="4" t="n">
-        <v>0.0561</v>
+        <v>0.0543</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>15866.96</v>
+        <v>9693.08</v>
       </c>
       <c r="I238" s="3" t="n">
         <v>330</v>
@@ -8821,16 +8821,16 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F239" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G239" s="6" t="n">
-        <v>0.0592</v>
+        <v>0.0517</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>8702.4</v>
+        <v>10526.5</v>
       </c>
       <c r="I239" s="5" t="n">
         <v>1180</v>
@@ -8856,16 +8856,16 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F240" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>0.0639</v>
+        <v>0.0517</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>16718.75</v>
+        <v>14262.93</v>
       </c>
       <c r="I240" s="3" t="n">
         <v>660</v>
@@ -8891,16 +8891,16 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F241" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G241" s="6" t="n">
-        <v>0.057</v>
+        <v>0.0517</v>
       </c>
       <c r="H241" s="5" t="n">
-        <v>15851.83</v>
+        <v>9720.42</v>
       </c>
       <c r="I241" s="5" t="n">
         <v>330</v>
@@ -8926,16 +8926,16 @@
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F242" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G242" s="4" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>6985.6</v>
+        <v>10500.6</v>
       </c>
       <c r="I242" s="3" t="n">
         <v>1180</v>
@@ -8961,16 +8961,16 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F243" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G243" s="6" t="n">
-        <v>0.0544</v>
+        <v>0.054</v>
       </c>
       <c r="H243" s="5" t="n">
-        <v>14221.82</v>
+        <v>15117.08</v>
       </c>
       <c r="I243" s="5" t="n">
         <v>660</v>
@@ -8996,16 +8996,16 @@
         </is>
       </c>
       <c r="E244" s="2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F244" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G244" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.054</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>8022.62</v>
+        <v>16006.32</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>660</v>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F245" s="5" t="n">
         <v>410</v>
@@ -9040,7 +9040,7 @@
         <v>0.054</v>
       </c>
       <c r="H245" s="5" t="n">
-        <v>15902.26</v>
+        <v>10472.22</v>
       </c>
       <c r="I245" s="5" t="n">
         <v>330</v>
@@ -9066,16 +9066,16 @@
         </is>
       </c>
       <c r="E246" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F246" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>0.0494</v>
+        <v>0.0457</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>19344.71</v>
+        <v>10593.1</v>
       </c>
       <c r="I246" s="3" t="n">
         <v>1180</v>
@@ -9107,10 +9107,10 @@
         <v>1850</v>
       </c>
       <c r="G247" s="6" t="n">
-        <v>0.0488</v>
+        <v>0.0457</v>
       </c>
       <c r="H247" s="5" t="n">
-        <v>12318.04</v>
+        <v>12358.62</v>
       </c>
       <c r="I247" s="5" t="n">
         <v>1180</v>
@@ -9136,16 +9136,16 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F248" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>0.0463</v>
+        <v>0.0457</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>26894.34</v>
+        <v>15250.25</v>
       </c>
       <c r="I248" s="3" t="n">
         <v>660</v>
@@ -9171,16 +9171,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F249" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G249" s="6" t="n">
-        <v>0.0455</v>
+        <v>0.0457</v>
       </c>
       <c r="H249" s="5" t="n">
-        <v>11349.01</v>
+        <v>10564.47</v>
       </c>
       <c r="I249" s="5" t="n">
         <v>330</v>
@@ -9206,16 +9206,16 @@
         </is>
       </c>
       <c r="E250" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F250" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G250" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.0565</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>12165.23</v>
+        <v>10472.85</v>
       </c>
       <c r="I250" s="3" t="n">
         <v>1180</v>
@@ -9241,16 +9241,16 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F251" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G251" s="6" t="n">
-        <v>0.0599</v>
+        <v>0.0565</v>
       </c>
       <c r="H251" s="5" t="n">
-        <v>14139.1</v>
+        <v>15077.13</v>
       </c>
       <c r="I251" s="5" t="n">
         <v>660</v>
@@ -9276,16 +9276,16 @@
         </is>
       </c>
       <c r="E252" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F252" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>0.0648</v>
+        <v>0.0565</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>9585.799999999999</v>
+        <v>10444.55</v>
       </c>
       <c r="I252" s="3" t="n">
         <v>330</v>
@@ -9311,16 +9311,16 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F253" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G253" s="6" t="n">
-        <v>0.0596</v>
+        <v>0.0565</v>
       </c>
       <c r="H253" s="5" t="n">
-        <v>12338.05</v>
+        <v>10831.38</v>
       </c>
       <c r="I253" s="5" t="n">
         <v>330</v>
@@ -9346,16 +9346,16 @@
         </is>
       </c>
       <c r="E254" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F254" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>0.1617</v>
+        <v>0.1285</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>4652.57</v>
+        <v>16122.75</v>
       </c>
       <c r="I254" s="3" t="n">
         <v>1180</v>
@@ -9381,16 +9381,16 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F255" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G255" s="6" t="n">
-        <v>0.1557</v>
+        <v>0.1285</v>
       </c>
       <c r="H255" s="5" t="n">
-        <v>13491.91</v>
+        <v>21299.46</v>
       </c>
       <c r="I255" s="5" t="n">
         <v>660</v>
@@ -9416,16 +9416,16 @@
         </is>
       </c>
       <c r="E256" s="2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F256" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>0.154</v>
+        <v>0.1285</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>10338.12</v>
+        <v>22118.67</v>
       </c>
       <c r="I256" s="3" t="n">
         <v>660</v>
@@ -9451,16 +9451,16 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F257" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G257" s="6" t="n">
-        <v>0.1547</v>
+        <v>0.1285</v>
       </c>
       <c r="H257" s="5" t="n">
-        <v>9357.469999999999</v>
+        <v>14292.6</v>
       </c>
       <c r="I257" s="5" t="n">
         <v>330</v>
@@ -9486,16 +9486,16 @@
         </is>
       </c>
       <c r="E258" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F258" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>0.052</v>
+        <v>0.0532</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>12276.6</v>
+        <v>10509.85</v>
       </c>
       <c r="I258" s="3" t="n">
         <v>1180</v>
@@ -9521,16 +9521,16 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F259" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G259" s="6" t="n">
-        <v>0.05</v>
+        <v>0.0532</v>
       </c>
       <c r="H259" s="5" t="n">
-        <v>10545</v>
+        <v>12261.49</v>
       </c>
       <c r="I259" s="5" t="n">
         <v>1180</v>
@@ -9556,16 +9556,16 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F260" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>0.0487</v>
+        <v>0.0532</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>7153.78</v>
+        <v>15130.4</v>
       </c>
       <c r="I260" s="3" t="n">
         <v>660</v>
@@ -9591,16 +9591,16 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F261" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G261" s="6" t="n">
-        <v>0.0492</v>
+        <v>0.0532</v>
       </c>
       <c r="H261" s="5" t="n">
-        <v>8937.52</v>
+        <v>16020.42</v>
       </c>
       <c r="I261" s="5" t="n">
         <v>660</v>
@@ -9626,16 +9626,16 @@
         </is>
       </c>
       <c r="E262" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F262" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G262" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.0532</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>12876.5</v>
+        <v>10481.44</v>
       </c>
       <c r="I262" s="3" t="n">
         <v>330</v>
@@ -9661,16 +9661,16 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F263" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G263" s="6" t="n">
-        <v>0.0564</v>
+        <v>0.044</v>
       </c>
       <c r="H263" s="5" t="n">
-        <v>5236.98</v>
+        <v>10611.6</v>
       </c>
       <c r="I263" s="5" t="n">
         <v>1180</v>
@@ -9696,16 +9696,16 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F264" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G264" s="4" t="n">
-        <v>0.0559</v>
+        <v>0.044</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>24848.71</v>
+        <v>15276.88</v>
       </c>
       <c r="I264" s="3" t="n">
         <v>660</v>
@@ -9731,16 +9731,16 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F265" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G265" s="6" t="n">
-        <v>0.0617</v>
+        <v>0.044</v>
       </c>
       <c r="H265" s="5" t="n">
-        <v>12695.2</v>
+        <v>10582.92</v>
       </c>
       <c r="I265" s="5" t="n">
         <v>330</v>
@@ -9766,16 +9766,16 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F266" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G266" s="4" t="n">
-        <v>0.1553</v>
+        <v>0.1435</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>7813.48</v>
+        <v>12676.2</v>
       </c>
       <c r="I266" s="3" t="n">
         <v>1180</v>
@@ -9801,16 +9801,16 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F267" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G267" s="6" t="n">
-        <v>0.1563</v>
+        <v>0.1435</v>
       </c>
       <c r="H267" s="5" t="n">
-        <v>23792.34</v>
+        <v>17712.42</v>
       </c>
       <c r="I267" s="5" t="n">
         <v>660</v>
@@ -9836,16 +9836,16 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F268" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>0.1531</v>
+        <v>0.1435</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>21494.32</v>
+        <v>18517.53</v>
       </c>
       <c r="I268" s="3" t="n">
         <v>660</v>
@@ -9871,16 +9871,16 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F269" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G269" s="6" t="n">
-        <v>0.1558</v>
+        <v>0.1435</v>
       </c>
       <c r="H269" s="5" t="n">
-        <v>8653.049999999999</v>
+        <v>11939.61</v>
       </c>
       <c r="I269" s="5" t="n">
         <v>330</v>
@@ -9906,16 +9906,16 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F270" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G270" s="4" t="n">
-        <v>0.0472</v>
+        <v>0.0548</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>17626.8</v>
+        <v>10491.35</v>
       </c>
       <c r="I270" s="3" t="n">
         <v>1180</v>
@@ -9941,16 +9941,16 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F271" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G271" s="6" t="n">
-        <v>0.0511</v>
+        <v>0.0548</v>
       </c>
       <c r="H271" s="5" t="n">
-        <v>24083.08</v>
+        <v>15103.76</v>
       </c>
       <c r="I271" s="5" t="n">
         <v>660</v>
@@ -9976,16 +9976,16 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F272" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G272" s="4" t="n">
-        <v>0.0526</v>
+        <v>0.0548</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>6214.94</v>
+        <v>10463</v>
       </c>
       <c r="I272" s="3" t="n">
         <v>330</v>
@@ -10011,16 +10011,16 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F273" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G273" s="6" t="n">
-        <v>0.0531</v>
+        <v>0.0548</v>
       </c>
       <c r="H273" s="5" t="n">
-        <v>14364.47</v>
+        <v>10850.51</v>
       </c>
       <c r="I273" s="5" t="n">
         <v>330</v>
@@ -10046,16 +10046,16 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F274" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G274" s="4" t="n">
-        <v>0.0469</v>
+        <v>0.0465</v>
       </c>
       <c r="H274" s="3" t="n">
-        <v>15869.12</v>
+        <v>10583.85</v>
       </c>
       <c r="I274" s="3" t="n">
         <v>1180</v>
@@ -10081,16 +10081,16 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F275" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G275" s="6" t="n">
-        <v>0.0421</v>
+        <v>0.0465</v>
       </c>
       <c r="H275" s="5" t="n">
-        <v>19493.26</v>
+        <v>12347.83</v>
       </c>
       <c r="I275" s="5" t="n">
         <v>1180</v>
@@ -10116,16 +10116,16 @@
         </is>
       </c>
       <c r="E276" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F276" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G276" s="4" t="n">
-        <v>0.047</v>
+        <v>0.0465</v>
       </c>
       <c r="H276" s="3" t="n">
-        <v>21499.68</v>
+        <v>15236.93</v>
       </c>
       <c r="I276" s="3" t="n">
         <v>660</v>
@@ -10151,16 +10151,16 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F277" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G277" s="6" t="n">
-        <v>0.0477</v>
+        <v>0.0465</v>
       </c>
       <c r="H277" s="5" t="n">
-        <v>12884.62</v>
+        <v>10555.25</v>
       </c>
       <c r="I277" s="5" t="n">
         <v>330</v>
@@ -10182,23 +10182,23 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Padrão</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E278" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F278" s="3" t="n">
-        <v>940</v>
+        <v>1850</v>
       </c>
       <c r="G278" s="4" t="n">
-        <v>0.0596</v>
+        <v>0.049</v>
       </c>
       <c r="H278" s="3" t="n">
-        <v>7071.81</v>
+        <v>5278.05</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>660</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="279">
@@ -10217,23 +10217,23 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Padrão</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>940</v>
+        <v>1850</v>
       </c>
       <c r="G279" s="6" t="n">
-        <v>0.0594</v>
+        <v>0.049</v>
       </c>
       <c r="H279" s="5" t="n">
-        <v>22988.26</v>
+        <v>5278.05</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>660</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="280">
@@ -10252,23 +10252,23 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Padrão</t>
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F280" s="3" t="n">
-        <v>410</v>
+        <v>940</v>
       </c>
       <c r="G280" s="4" t="n">
-        <v>0.0585</v>
+        <v>0.049</v>
       </c>
       <c r="H280" s="3" t="n">
-        <v>14282.56</v>
+        <v>21454.56</v>
       </c>
       <c r="I280" s="3" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="281">
@@ -10287,23 +10287,23 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Padrão</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F281" s="5" t="n">
-        <v>410</v>
+        <v>940</v>
       </c>
       <c r="G281" s="6" t="n">
-        <v>0.0581</v>
+        <v>0.049</v>
       </c>
       <c r="H281" s="5" t="n">
-        <v>14288.62</v>
+        <v>22348.5</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="282">
@@ -10326,16 +10326,16 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="F282" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>0.0532</v>
+        <v>0.049</v>
       </c>
       <c r="H282" s="3" t="n">
-        <v>6599.2</v>
+        <v>46009.38</v>
       </c>
       <c r="I282" s="3" t="n">
         <v>330</v>
@@ -10361,16 +10361,16 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F283" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G283" s="6" t="n">
-        <v>0.0541</v>
+        <v>0.0557</v>
       </c>
       <c r="H283" s="5" t="n">
-        <v>8749.57</v>
+        <v>10482.1</v>
       </c>
       <c r="I283" s="5" t="n">
         <v>1180</v>
@@ -10396,16 +10396,16 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F284" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G284" s="4" t="n">
-        <v>0.052</v>
+        <v>0.0557</v>
       </c>
       <c r="H284" s="3" t="n">
-        <v>9802.32</v>
+        <v>15090.45</v>
       </c>
       <c r="I284" s="3" t="n">
         <v>660</v>
@@ -10431,16 +10431,16 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F285" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G285" s="6" t="n">
-        <v>0.0535</v>
+        <v>0.0557</v>
       </c>
       <c r="H285" s="5" t="n">
-        <v>19573.62</v>
+        <v>15978.12</v>
       </c>
       <c r="I285" s="5" t="n">
         <v>660</v>
@@ -10466,16 +10466,16 @@
         </is>
       </c>
       <c r="E286" s="2" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F286" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G286" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0557</v>
       </c>
       <c r="H286" s="3" t="n">
-        <v>13643.98</v>
+        <v>10453.77</v>
       </c>
       <c r="I286" s="3" t="n">
         <v>330</v>
@@ -10501,16 +10501,16 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F287" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G287" s="6" t="n">
-        <v>0.0614</v>
+        <v>0.0523</v>
       </c>
       <c r="H287" s="5" t="n">
-        <v>19100.51</v>
+        <v>10519.1</v>
       </c>
       <c r="I287" s="5" t="n">
         <v>1180</v>
@@ -10536,16 +10536,16 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F288" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G288" s="4" t="n">
-        <v>0.0581</v>
+        <v>0.0523</v>
       </c>
       <c r="H288" s="3" t="n">
-        <v>20363.88</v>
+        <v>15143.71</v>
       </c>
       <c r="I288" s="3" t="n">
         <v>660</v>
@@ -10571,16 +10571,16 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F289" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G289" s="6" t="n">
-        <v>0.0624</v>
+        <v>0.0523</v>
       </c>
       <c r="H289" s="5" t="n">
-        <v>11148.06</v>
+        <v>10490.67</v>
       </c>
       <c r="I289" s="5" t="n">
         <v>330</v>
@@ -10606,16 +10606,16 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F290" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G290" s="4" t="n">
-        <v>0.0582</v>
+        <v>0.055</v>
       </c>
       <c r="H290" s="3" t="n">
-        <v>19165.63</v>
+        <v>10489.5</v>
       </c>
       <c r="I290" s="3" t="n">
         <v>1180</v>
@@ -10641,16 +10641,16 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F291" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G291" s="6" t="n">
-        <v>0.0563</v>
+        <v>0.055</v>
       </c>
       <c r="H291" s="5" t="n">
-        <v>8870.780000000001</v>
+        <v>15101.1</v>
       </c>
       <c r="I291" s="5" t="n">
         <v>660</v>
@@ -10676,16 +10676,16 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F292" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G292" s="4" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="H292" s="3" t="n">
-        <v>8864.200000000001</v>
+        <v>15101.1</v>
       </c>
       <c r="I292" s="3" t="n">
         <v>660</v>
@@ -10711,16 +10711,16 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F293" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G293" s="6" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="H293" s="5" t="n">
-        <v>11648.1</v>
+        <v>10073.7</v>
       </c>
       <c r="I293" s="5" t="n">
         <v>330</v>
@@ -10746,16 +10746,16 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F294" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G294" s="4" t="n">
-        <v>0.0508</v>
+        <v>0.045</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>7024.08</v>
+        <v>10600.5</v>
       </c>
       <c r="I294" s="3" t="n">
         <v>1180</v>
@@ -10787,10 +10787,10 @@
         <v>1850</v>
       </c>
       <c r="G295" s="6" t="n">
-        <v>0.0498</v>
+        <v>0.045</v>
       </c>
       <c r="H295" s="5" t="n">
-        <v>10547.22</v>
+        <v>10600.5</v>
       </c>
       <c r="I295" s="5" t="n">
         <v>1180</v>
@@ -10816,16 +10816,16 @@
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F296" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G296" s="4" t="n">
-        <v>0.0458</v>
+        <v>0.045</v>
       </c>
       <c r="H296" s="3" t="n">
-        <v>12557.27</v>
+        <v>15260.9</v>
       </c>
       <c r="I296" s="3" t="n">
         <v>660</v>
@@ -10851,16 +10851,16 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F297" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G297" s="6" t="n">
-        <v>0.0518</v>
+        <v>0.045</v>
       </c>
       <c r="H297" s="5" t="n">
-        <v>13606.67</v>
+        <v>10180.3</v>
       </c>
       <c r="I297" s="5" t="n">
         <v>330</v>
@@ -10886,16 +10886,16 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F298" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G298" s="4" t="n">
-        <v>0.0638</v>
+        <v>0.058</v>
       </c>
       <c r="H298" s="3" t="n">
-        <v>17319.7</v>
+        <v>10456.2</v>
       </c>
       <c r="I298" s="3" t="n">
         <v>1180</v>
@@ -10921,16 +10921,16 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F299" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G299" s="6" t="n">
-        <v>0.0608</v>
+        <v>0.058</v>
       </c>
       <c r="H299" s="5" t="n">
-        <v>8828.48</v>
+        <v>15053.16</v>
       </c>
       <c r="I299" s="5" t="n">
         <v>660</v>
@@ -10956,16 +10956,16 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F300" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>0.0593</v>
+        <v>0.058</v>
       </c>
       <c r="H300" s="3" t="n">
-        <v>13884.73</v>
+        <v>10041.72</v>
       </c>
       <c r="I300" s="3" t="n">
         <v>330</v>
@@ -10991,16 +10991,16 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F301" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G301" s="6" t="n">
-        <v>0.0619</v>
+        <v>0.058</v>
       </c>
       <c r="H301" s="5" t="n">
-        <v>6153.94</v>
+        <v>10427.94</v>
       </c>
       <c r="I301" s="5" t="n">
         <v>330</v>
@@ -11026,16 +11026,16 @@
         </is>
       </c>
       <c r="E302" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F302" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G302" s="4" t="n">
-        <v>0.1846</v>
+        <v>0.155</v>
       </c>
       <c r="H302" s="3" t="n">
-        <v>9050.940000000001</v>
+        <v>14069.25</v>
       </c>
       <c r="I302" s="3" t="n">
         <v>1180</v>
@@ -11061,16 +11061,16 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F303" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G303" s="6" t="n">
-        <v>0.1867</v>
+        <v>0.155</v>
       </c>
       <c r="H303" s="5" t="n">
-        <v>9174.02</v>
+        <v>19857.5</v>
       </c>
       <c r="I303" s="5" t="n">
         <v>660</v>
@@ -11096,16 +11096,16 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F304" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G304" s="4" t="n">
-        <v>0.1899</v>
+        <v>0.155</v>
       </c>
       <c r="H304" s="3" t="n">
-        <v>21321.83</v>
+        <v>20651.8</v>
       </c>
       <c r="I304" s="3" t="n">
         <v>660</v>
@@ -11131,16 +11131,16 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F305" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G305" s="6" t="n">
-        <v>0.189</v>
+        <v>0.155</v>
       </c>
       <c r="H305" s="5" t="n">
-        <v>7980.24</v>
+        <v>13165.1</v>
       </c>
       <c r="I305" s="5" t="n">
         <v>330</v>
@@ -11166,16 +11166,16 @@
         </is>
       </c>
       <c r="E306" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F306" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G306" s="4" t="n">
-        <v>0.0481</v>
+        <v>0.054</v>
       </c>
       <c r="H306" s="3" t="n">
-        <v>8805.07</v>
+        <v>10500.6</v>
       </c>
       <c r="I306" s="3" t="n">
         <v>1180</v>
@@ -11201,16 +11201,16 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F307" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G307" s="6" t="n">
-        <v>0.0519</v>
+        <v>0.054</v>
       </c>
       <c r="H307" s="5" t="n">
-        <v>5261.95</v>
+        <v>10500.6</v>
       </c>
       <c r="I307" s="5" t="n">
         <v>1180</v>
@@ -11236,16 +11236,16 @@
         </is>
       </c>
       <c r="E308" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F308" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G308" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.054</v>
       </c>
       <c r="H308" s="3" t="n">
-        <v>25929.71</v>
+        <v>15117.08</v>
       </c>
       <c r="I308" s="3" t="n">
         <v>660</v>
@@ -11271,16 +11271,16 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F309" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G309" s="6" t="n">
-        <v>0.0534</v>
+        <v>0.054</v>
       </c>
       <c r="H309" s="5" t="n">
-        <v>12457.26</v>
+        <v>15117.08</v>
       </c>
       <c r="I309" s="5" t="n">
         <v>660</v>
@@ -11306,16 +11306,16 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F310" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G310" s="4" t="n">
-        <v>0.0537</v>
+        <v>0.054</v>
       </c>
       <c r="H310" s="3" t="n">
-        <v>9311.59</v>
+        <v>10084.36</v>
       </c>
       <c r="I310" s="3" t="n">
         <v>330</v>
@@ -11341,16 +11341,16 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F311" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G311" s="6" t="n">
-        <v>0.0577</v>
+        <v>0.043</v>
       </c>
       <c r="H311" s="5" t="n">
-        <v>12202.78</v>
+        <v>10622.7</v>
       </c>
       <c r="I311" s="5" t="n">
         <v>1180</v>
@@ -11376,16 +11376,16 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F312" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G312" s="4" t="n">
-        <v>0.0601</v>
+        <v>0.043</v>
       </c>
       <c r="H312" s="3" t="n">
-        <v>19437.13</v>
+        <v>15292.86</v>
       </c>
       <c r="I312" s="3" t="n">
         <v>660</v>
@@ -11411,16 +11411,16 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F313" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G313" s="6" t="n">
-        <v>0.0584</v>
+        <v>0.043</v>
       </c>
       <c r="H313" s="5" t="n">
-        <v>16600.41</v>
+        <v>10201.62</v>
       </c>
       <c r="I313" s="5" t="n">
         <v>330</v>
@@ -11446,16 +11446,16 @@
         </is>
       </c>
       <c r="E314" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F314" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G314" s="4" t="n">
-        <v>0.1878</v>
+        <v>0.175</v>
       </c>
       <c r="H314" s="3" t="n">
-        <v>10517.99</v>
+        <v>12210</v>
       </c>
       <c r="I314" s="3" t="n">
         <v>1180</v>
@@ -11481,16 +11481,16 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F315" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G315" s="6" t="n">
-        <v>0.1801</v>
+        <v>0.175</v>
       </c>
       <c r="H315" s="5" t="n">
-        <v>17726.24</v>
+        <v>16285.5</v>
       </c>
       <c r="I315" s="5" t="n">
         <v>660</v>
@@ -11522,10 +11522,10 @@
         <v>940</v>
       </c>
       <c r="G316" s="4" t="n">
-        <v>0.1806</v>
+        <v>0.175</v>
       </c>
       <c r="H316" s="3" t="n">
-        <v>16945.19</v>
+        <v>17061</v>
       </c>
       <c r="I316" s="3" t="n">
         <v>660</v>
@@ -11551,16 +11551,16 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F317" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G317" s="6" t="n">
-        <v>0.1877</v>
+        <v>0.175</v>
       </c>
       <c r="H317" s="5" t="n">
-        <v>10324.33</v>
+        <v>10824</v>
       </c>
       <c r="I317" s="5" t="n">
         <v>330</v>
@@ -11586,16 +11586,16 @@
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F318" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G318" s="4" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="H318" s="3" t="n">
-        <v>17501</v>
+        <v>10478.4</v>
       </c>
       <c r="I318" s="3" t="n">
         <v>1180</v>
@@ -11621,16 +11621,16 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F319" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G319" s="6" t="n">
-        <v>0.0477</v>
+        <v>0.056</v>
       </c>
       <c r="H319" s="5" t="n">
-        <v>17903.24</v>
+        <v>15085.12</v>
       </c>
       <c r="I319" s="5" t="n">
         <v>660</v>
@@ -11656,16 +11656,16 @@
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F320" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G320" s="4" t="n">
-        <v>0.0534</v>
+        <v>0.056</v>
       </c>
       <c r="H320" s="3" t="n">
-        <v>17464.77</v>
+        <v>10063.04</v>
       </c>
       <c r="I320" s="3" t="n">
         <v>330</v>
@@ -11691,16 +11691,16 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F321" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G321" s="6" t="n">
-        <v>0.0507</v>
+        <v>0.056</v>
       </c>
       <c r="H321" s="5" t="n">
-        <v>6616.62</v>
+        <v>10450.08</v>
       </c>
       <c r="I321" s="5" t="n">
         <v>330</v>
@@ -11726,16 +11726,16 @@
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F322" s="3" t="n">
         <v>1850</v>
       </c>
       <c r="G322" s="4" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="H322" s="3" t="n">
-        <v>8815.25</v>
+        <v>10589.4</v>
       </c>
       <c r="I322" s="3" t="n">
         <v>1180</v>
@@ -11761,16 +11761,16 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F323" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G323" s="6" t="n">
-        <v>0.0486</v>
+        <v>0.046</v>
       </c>
       <c r="H323" s="5" t="n">
-        <v>12320.63</v>
+        <v>10589.4</v>
       </c>
       <c r="I323" s="5" t="n">
         <v>1180</v>
@@ -11796,16 +11796,16 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F324" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G324" s="4" t="n">
-        <v>0.0458</v>
+        <v>0.046</v>
       </c>
       <c r="H324" s="3" t="n">
-        <v>10763.38</v>
+        <v>15244.92</v>
       </c>
       <c r="I324" s="3" t="n">
         <v>660</v>
@@ -11831,16 +11831,16 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F325" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G325" s="6" t="n">
-        <v>0.0451</v>
+        <v>0.046</v>
       </c>
       <c r="H325" s="5" t="n">
-        <v>13702.81</v>
+        <v>10169.64</v>
       </c>
       <c r="I325" s="5" t="n">
         <v>330</v>
@@ -11862,23 +11862,23 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Padrão</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F326" s="3" t="n">
-        <v>940</v>
+        <v>1850</v>
       </c>
       <c r="G326" s="4" t="n">
-        <v>0.0586</v>
+        <v>0.049</v>
       </c>
       <c r="H326" s="3" t="n">
-        <v>9734.08</v>
+        <v>1759.35</v>
       </c>
       <c r="I326" s="3" t="n">
-        <v>660</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="327">
@@ -11897,23 +11897,23 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Padrão</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>940</v>
+        <v>1850</v>
       </c>
       <c r="G327" s="6" t="n">
-        <v>0.057</v>
+        <v>0.049</v>
       </c>
       <c r="H327" s="5" t="n">
-        <v>13296.3</v>
+        <v>1759.35</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>660</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="328">
@@ -11932,23 +11932,23 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Padrão</t>
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>410</v>
+        <v>940</v>
       </c>
       <c r="G328" s="4" t="n">
-        <v>0.0569</v>
+        <v>0.049</v>
       </c>
       <c r="H328" s="3" t="n">
-        <v>16626.85</v>
+        <v>19666.68</v>
       </c>
       <c r="I328" s="3" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="329">
@@ -11967,23 +11967,23 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Padrão</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>410</v>
+        <v>940</v>
       </c>
       <c r="G329" s="6" t="n">
-        <v>0.0543</v>
+        <v>0.049</v>
       </c>
       <c r="H329" s="5" t="n">
-        <v>5816.06</v>
+        <v>20560.62</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="330">
@@ -12006,16 +12006,16 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="F330" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G330" s="4" t="n">
-        <v>0.0569</v>
+        <v>0.049</v>
       </c>
       <c r="H330" s="3" t="n">
-        <v>17400.19</v>
+        <v>53807.58</v>
       </c>
       <c r="I330" s="3" t="n">
         <v>330</v>
@@ -12041,16 +12041,16 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F331" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G331" s="6" t="n">
-        <v>0.0522</v>
+        <v>0.057</v>
       </c>
       <c r="H331" s="5" t="n">
-        <v>17534.3</v>
+        <v>10467.3</v>
       </c>
       <c r="I331" s="5" t="n">
         <v>1180</v>
@@ -12076,16 +12076,16 @@
         </is>
       </c>
       <c r="E332" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F332" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G332" s="4" t="n">
-        <v>0.0523</v>
+        <v>0.057</v>
       </c>
       <c r="H332" s="3" t="n">
-        <v>10690.06</v>
+        <v>15069.14</v>
       </c>
       <c r="I332" s="3" t="n">
         <v>660</v>
@@ -12111,16 +12111,16 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F333" s="5" t="n">
         <v>940</v>
       </c>
       <c r="G333" s="6" t="n">
-        <v>0.0515</v>
+        <v>0.057</v>
       </c>
       <c r="H333" s="5" t="n">
-        <v>17831.8</v>
+        <v>15069.14</v>
       </c>
       <c r="I333" s="5" t="n">
         <v>660</v>
@@ -12146,16 +12146,16 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F334" s="3" t="n">
         <v>410</v>
       </c>
       <c r="G334" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.057</v>
       </c>
       <c r="H334" s="3" t="n">
-        <v>15940.92</v>
+        <v>10052.38</v>
       </c>
       <c r="I334" s="3" t="n">
         <v>330</v>
@@ -12181,16 +12181,16 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F335" s="5" t="n">
         <v>1850</v>
       </c>
       <c r="G335" s="6" t="n">
-        <v>0.062</v>
+        <v>0.053</v>
       </c>
       <c r="H335" s="5" t="n">
-        <v>13882.4</v>
+        <v>10511.7</v>
       </c>
       <c r="I335" s="5" t="n">
         <v>1180</v>
@@ -12216,16 +12216,16 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F336" s="3" t="n">
         <v>940</v>
       </c>
       <c r="G336" s="4" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>17728.4</v>
+        <v>15133.06</v>
       </c>
       <c r="I336" s="3" t="n">
         <v>660</v>
@@ -12251,16 +12251,16 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F337" s="5" t="n">
         <v>410</v>
       </c>
       <c r="G337" s="6" t="n">
-        <v>0.0576</v>
+        <v>0.053</v>
       </c>
       <c r="H337" s="5" t="n">
-        <v>17000.9</v>
+        <v>10095.02</v>
       </c>
       <c r="I337" s="5" t="n">
         <v>330</v>
@@ -12340,7 +12340,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   média das margens de cada pedido    trata um pedido de 3 itens igual a um de 45</t>
+          <t xml:space="preserve">   média das margens de cada pedido    trata um pedido pequeno igual a um grande</t>
         </is>
       </c>
     </row>
